--- a/Testkit_Q1_PRN222/Q12/Header.xlsx
+++ b/Testkit_Q1_PRN222/Q12/Header.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83E0466-22FF-46A2-A9BA-89307440A7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2137733-8AE0-4642-8A22-B1809C619EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataPattern" sheetId="3" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="TestSuite" sheetId="1" r:id="rId3"/>
     <sheet name="Config" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>Data Type</t>
   </si>
@@ -101,12 +101,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -177,12 +176,12 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -466,14 +465,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.36328125" customWidth="1"/>
-    <col min="2" max="2" width="22.1796875" customWidth="1"/>
-    <col min="3" max="3" width="21.90625" customWidth="1"/>
+    <col min="1" max="1" width="18.3984375" customWidth="1"/>
+    <col min="2" max="2" width="22.19921875" customWidth="1"/>
+    <col min="3" max="3" width="21.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,7 +480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -492,19 +491,18 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14" s="5" customFormat="1">
+    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -512,72 +510,71 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>7</v>
+      <c r="B7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" customWidth="1" style="5"/>
-    <col min="2" max="2" width="44.36328125" customWidth="1" style="5"/>
-    <col min="3" max="4" width="8.90625" customWidth="1" style="5"/>
-    <col min="5" max="16384" width="8.90625" customWidth="1" style="5"/>
+    <col min="1" max="1" width="10.59765625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="44.3984375" style="5" customWidth="1"/>
+    <col min="3" max="5" width="8.8984375" style="5" customWidth="1"/>
+    <col min="6" max="16384" width="8.8984375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>13</v>
       </c>
@@ -585,7 +582,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -593,7 +590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
@@ -601,7 +598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -609,7 +606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
@@ -617,7 +614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -625,7 +622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
@@ -636,19 +633,18 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C6C48B-55C0-4A7D-A267-4474B31A4631}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" bestFit="1" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14" s="5" customFormat="1">
+    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
@@ -656,24 +652,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Testkit_Q1_PRN222/Q12/Header.xlsx
+++ b/Testkit_Q1_PRN222/Q12/Header.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2137733-8AE0-4642-8A22-B1809C619EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E8382B-EB79-4047-99B4-7A5F812A7EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataPattern" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>Data Type</t>
   </si>
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>TCP</t>
+  </si>
+  <si>
+    <t>Grade_Content</t>
+  </si>
+  <si>
+    <t>Client</t>
   </si>
 </sst>
 </file>
@@ -638,9 +644,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C6C48B-55C0-4A7D-A267-4474B31A4631}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="13.3984375" customWidth="1"/>
     <col min="2" max="2" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -668,6 +675,14 @@
         <v>20</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Testkit_Q1_PRN222/Q12/Header.xlsx
+++ b/Testkit_Q1_PRN222/Q12/Header.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E8382B-EB79-4047-99B4-7A5F812A7EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D623F9D5-D9DA-4661-9BB3-0FBDE8312E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
     <t>Grade_Content</t>
   </si>
   <si>
-    <t>Client</t>
+    <t>Server</t>
   </si>
 </sst>
 </file>
